--- a/test_data/WTA Information/WTA Information_Test_Cases.xlsx
+++ b/test_data/WTA Information/WTA Information_Test_Cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -512,7 +512,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Information_01</t>
+          <t>Information_02</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,17 +522,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Information workspace loads with the Jurisdictions and Categories panel</t>
+          <t>Switching region tabs changes the visible country list</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>The /wta/Information page must show the left jurisdiction/category panel and the 'Select Jurisdictions and Categories' placeholder in the content area.</t>
+          <t>Clicking the 'Americas' region tab must show Americas countries and hide Asia Pacific-only countries (e.g. 'Australia').</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>User is logged in.</t>
+          <t>User is logged in and on the Information workspace, 'Asia Pacific' selected by default.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -541,65 +541,6 @@
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in
-2. Navigate to Information (already the post-login landing page)
-3. Verify the panel heading and placeholder text are visible</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>The /wta/Information page must show the left jurisdiction/category panel and the 'Select Jurisdictions and Categories' placeholder in the content area.</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>The Information workspace loaded on /wta/Information with the 'Select Jurisdictions and Categories' heading and instruction text visible.</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Information workspace shows its panel heading and placeholder</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Information_02</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>WTA Information</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Switching region tabs changes the visible country list</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Clicking the 'Americas' region tab must show Americas countries and hide Asia Pacific-only countries (e.g. 'Australia').</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the Information workspace, 'Asia Pacific' selected by default.</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Verify 'Australia' (Asia Pacific) is visible
@@ -607,19 +548,79 @@
 4. Verify 'Australia' is no longer visible in the list</t>
         </is>
       </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Clicking the 'Americas' region tab must show Americas countries and hide Asia Pacific-only countries (e.g. 'Australia').</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Switching from 'Asia Pacific' to 'Americas' changed the rendered country list (Australia disappeared).</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Australia' is visible under Asia Pacific and hidden after switching to Americas</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Information_03</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>WTA Information</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Country search filters the jurisdiction list</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Typing a country name into 'Search countries' must narrow the list to matches; a non-existent name must show a 'No countries found' message.</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the Information workspace.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Match: 'Japan' / No match: 'zzzznotarealcountry'</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Search for 'Japan', verify it is shown and 'Australia' is filtered out
+3. Search for a bogus name, verify the 'No countries found' message appears</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Clicking the 'Americas' region tab must show Americas countries and hide Asia Pacific-only countries (e.g. 'Australia').</t>
+          <t>Typing a country name into 'Search countries' must narrow the list to matches; a non-existent name must show a 'No countries found' message.</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Switching from 'Asia Pacific' to 'Americas' changed the rendered country list (Australia disappeared).</t>
+          <t>The country search box correctly filtered the list for a real match and showed a 'No countries found' message for a bogus search term.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>[PASS] 'Australia' is visible under Asia Pacific and hidden after switching to Americas</t>
+          <t>[PASS] Searching 'Japan' shows Japan and filters out Australia
+[PASS] A non-existent search term shows a 'No countries found' message</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -631,7 +632,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Information_03</t>
+          <t>Information_04</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,12 +642,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Country search filters the jurisdiction list</t>
+          <t>Selecting only a jurisdiction (no category) keeps the placeholder</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Typing a country name into 'Search countries' must narrow the list to matches; a non-existent name must show a 'No countries found' message.</t>
+          <t>Checking a country's checkbox without also selecting a category must NOT replace the 'Select Jurisdictions and Categories' placeholder - both are required.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -656,30 +657,29 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Match: 'Japan' / No match: 'zzzznotarealcountry'</t>
+          <t>Country: Australia</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1. Log in
-2. Search for 'Japan', verify it is shown and 'Australia' is filtered out
-3. Search for a bogus name, verify the 'No countries found' message appears</t>
+2. Check the 'Australia' checkbox only
+3. Verify the placeholder instruction text is still shown</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Typing a country name into 'Search countries' must narrow the list to matches; a non-existent name must show a 'No countries found' message.</t>
+          <t>Checking a country's checkbox without also selecting a category must NOT replace the 'Select Jurisdictions and Categories' placeholder - both are required.</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>The country search box correctly filtered the list for a real match and showed a 'No countries found' message for a bogus search term.</t>
+          <t>Selecting Australia's jurisdiction checkbox alone left the 'Select Jurisdictions and Categories' placeholder in place, confirming a category selection is also required to render content.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>[PASS] Searching 'Japan' shows Japan and filters out Australia
-[PASS] A non-existent search term shows a 'No countries found' message</t>
+          <t>[PASS] Placeholder remains visible after selecting a jurisdiction with no category</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -691,7 +691,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Information_04</t>
+          <t>Information_06</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -701,12 +701,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Selecting only a jurisdiction (no category) keeps the placeholder</t>
+          <t>'Check All' selects every category (not the country list)</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Checking a country's checkbox without also selecting a category must NOT replace the 'Select Jurisdictions and Categories' placeholder - both are required.</t>
+          <t>Clicking the 'Check All' checkbox (which sits in the CATEGORY tree, right above the 'Depth-' control) must check every category checkbox, including nested children, while leaving the country checklist untouched.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -716,128 +716,10 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Country: Australia</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in
-2. Check the 'Australia' checkbox only
-3. Verify the placeholder instruction text is still shown</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Checking a country's checkbox without also selecting a category must NOT replace the 'Select Jurisdictions and Categories' placeholder - both are required.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Selecting Australia's jurisdiction checkbox alone left the 'Select Jurisdictions and Categories' placeholder in place, confirming a category selection is also required to render content.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Placeholder remains visible after selecting a jurisdiction with no category</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Information_05</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>WTA Information</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Checking a parent category expands its child categories</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Checking the 'Liability to Tax' parent category must expand the tree in place to reveal its children (e.g. 'Residence').</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the Information workspace.</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Category: Liability to Tax</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in
-2. Check the 'Liability to Tax' category checkbox
-3. Verify a child category ('Residence') becomes visible</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Checking the 'Liability to Tax' parent category must expand the tree in place to reveal its children (e.g. 'Residence').</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Checking 'Liability to Tax' expanded the category tree, revealing the child category 'Residence'.</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] 'Residence' is hidden before and visible after expanding 'Liability to Tax'</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Information_06</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>WTA Information</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>'Check All' selects every category (not the country list)</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Clicking the 'Check All' checkbox (which sits in the CATEGORY tree, right above the 'Depth-' control) must check every category checkbox, including nested children, while leaving the country checklist untouched.</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the Information workspace.</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Click 'Check All'
@@ -845,23 +727,23 @@
 4. Verify the 'Australia' country checkbox is still unchecked (Check All only affects categories)</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Clicking the 'Check All' checkbox (which sits in the CATEGORY tree, right above the 'Depth-' control) must check every category checkbox, including nested children, while leaving the country checklist untouched.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Check All' checked every category (including nested children like 'Residence' under 'Liability to Tax') and left the country checklist untouched.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'Liability to Tax' and its child 'Residence' are checked after 'Check All'
 [PASS] 'Australia' remains unchecked - 'Check All' only applies to categories</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/test_data/WTA Information/WTA Information_Test_Cases.xlsx
+++ b/test_data/WTA Information/WTA Information_Test_Cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -512,35 +512,94 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>Information_01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>WTA Information</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Information workspace loads with the Jurisdictions and Categories panel</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>The /wta/Information page must show the left jurisdiction/category panel and the 'Select Jurisdictions and Categories' placeholder in the content area.</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Navigate to Information (already the post-login landing page)
+3. Verify the panel heading and placeholder text are visible</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>The /wta/Information page must show the left jurisdiction/category panel and the 'Select Jurisdictions and Categories' placeholder in the content area.</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>The Information workspace loaded on /wta/Information with the 'Select Jurisdictions and Categories' heading and instruction text visible.</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Information workspace shows its panel heading and placeholder</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
           <t>Information_02</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>WTA Information</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Switching region tabs changes the visible country list</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Clicking the 'Americas' region tab must show Americas countries and hide Asia Pacific-only countries (e.g. 'Australia').</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on the Information workspace, 'Asia Pacific' selected by default.</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Verify 'Australia' (Asia Pacific) is visible
@@ -548,178 +607,237 @@
 4. Verify 'Australia' is no longer visible in the list</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Clicking the 'Americas' region tab must show Americas countries and hide Asia Pacific-only countries (e.g. 'Australia').</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Switching from 'Asia Pacific' to 'Americas' changed the rendered country list (Australia disappeared).</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'Australia' is visible under Asia Pacific and hidden after switching to Americas</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Information_03</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>WTA Information</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Country search filters the jurisdiction list</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Typing a country name into 'Search countries' must narrow the list to matches; a non-existent name must show a 'No countries found' message.</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on the Information workspace.</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Match: 'Japan' / No match: 'zzzznotarealcountry'</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Search for 'Japan', verify it is shown and 'Australia' is filtered out
 3. Search for a bogus name, verify the 'No countries found' message appears</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Typing a country name into 'Search countries' must narrow the list to matches; a non-existent name must show a 'No countries found' message.</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>The country search box correctly filtered the list for a real match and showed a 'No countries found' message for a bogus search term.</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>[PASS] Searching 'Japan' shows Japan and filters out Australia
 [PASS] A non-existent search term shows a 'No countries found' message</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Information_04</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>WTA Information</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Selecting only a jurisdiction (no category) keeps the placeholder</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Checking a country's checkbox without also selecting a category must NOT replace the 'Select Jurisdictions and Categories' placeholder - both are required.</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on the Information workspace.</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Country: Australia</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Check the 'Australia' checkbox only
 3. Verify the placeholder instruction text is still shown</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Checking a country's checkbox without also selecting a category must NOT replace the 'Select Jurisdictions and Categories' placeholder - both are required.</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>Selecting Australia's jurisdiction checkbox alone left the 'Select Jurisdictions and Categories' placeholder in place, confirming a category selection is also required to render content.</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>[PASS] Placeholder remains visible after selecting a jurisdiction with no category</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Information_05</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>WTA Information</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Checking a parent category expands its child categories</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Checking the 'Liability to Tax' parent category must expand the tree in place to reveal its children (e.g. 'Residence').</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on the Information workspace.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Category: Liability to Tax</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Check the 'Liability to Tax' category checkbox
+3. Verify a child category ('Residence') becomes visible</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Checking the 'Liability to Tax' parent category must expand the tree in place to reveal its children (e.g. 'Residence').</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Checking 'Liability to Tax' expanded the category tree, revealing the child category 'Residence'.</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Residence' is hidden before and visible after expanding 'Liability to Tax'</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Information_06</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>WTA Information</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>'Check All' selects every category (not the country list)</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Clicking the 'Check All' checkbox (which sits in the CATEGORY tree, right above the 'Depth-' control) must check every category checkbox, including nested children, while leaving the country checklist untouched.</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on the Information workspace.</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Click 'Check All'
@@ -727,23 +845,23 @@
 4. Verify the 'Australia' country checkbox is still unchecked (Check All only affects categories)</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Clicking the 'Check All' checkbox (which sits in the CATEGORY tree, right above the 'Depth-' control) must check every category checkbox, including nested children, while leaving the country checklist untouched.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Check All' checked every category (including nested children like 'Residence' under 'Liability to Tax') and left the country checklist untouched.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'Liability to Tax' and its child 'Residence' are checked after 'Check All'
 [PASS] 'Australia' remains unchecked - 'Check All' only applies to categories</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/test_data/WTA Information/WTA Information_Test_Cases.xlsx
+++ b/test_data/WTA Information/WTA Information_Test_Cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -571,7 +571,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Information_02</t>
+          <t>Information_05</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -581,287 +581,47 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Switching region tabs changes the visible country list</t>
+          <t>Checking a parent category expands its child categories</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Clicking the 'Americas' region tab must show Americas countries and hide Asia Pacific-only countries (e.g. 'Australia').</t>
+          <t>Checking the 'Liability to Tax' parent category must expand the tree in place to reveal its children (e.g. 'Residence').</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and on the Information workspace, 'Asia Pacific' selected by default.</t>
+          <t>User is logged in and on the Information workspace.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Category: Liability to Tax</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in
-2. Verify 'Australia' (Asia Pacific) is visible
-3. Click the 'Americas' tab
-4. Verify 'Australia' is no longer visible in the list</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Clicking the 'Americas' region tab must show Americas countries and hide Asia Pacific-only countries (e.g. 'Australia').</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Switching from 'Asia Pacific' to 'Americas' changed the rendered country list (Australia disappeared).</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] 'Australia' is visible under Asia Pacific and hidden after switching to Americas</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Information_03</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>WTA Information</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Country search filters the jurisdiction list</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Typing a country name into 'Search countries' must narrow the list to matches; a non-existent name must show a 'No countries found' message.</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the Information workspace.</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Match: 'Japan' / No match: 'zzzznotarealcountry'</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in
-2. Search for 'Japan', verify it is shown and 'Australia' is filtered out
-3. Search for a bogus name, verify the 'No countries found' message appears</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Typing a country name into 'Search countries' must narrow the list to matches; a non-existent name must show a 'No countries found' message.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>The country search box correctly filtered the list for a real match and showed a 'No countries found' message for a bogus search term.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Searching 'Japan' shows Japan and filters out Australia
-[PASS] A non-existent search term shows a 'No countries found' message</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Information_04</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>WTA Information</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Selecting only a jurisdiction (no category) keeps the placeholder</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Checking a country's checkbox without also selecting a category must NOT replace the 'Select Jurisdictions and Categories' placeholder - both are required.</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the Information workspace.</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Country: Australia</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in
-2. Check the 'Australia' checkbox only
-3. Verify the placeholder instruction text is still shown</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Checking a country's checkbox without also selecting a category must NOT replace the 'Select Jurisdictions and Categories' placeholder - both are required.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Selecting Australia's jurisdiction checkbox alone left the 'Select Jurisdictions and Categories' placeholder in place, confirming a category selection is also required to render content.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Placeholder remains visible after selecting a jurisdiction with no category</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Information_05</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>WTA Information</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Checking a parent category expands its child categories</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Checking the 'Liability to Tax' parent category must expand the tree in place to reveal its children (e.g. 'Residence').</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the Information workspace.</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Category: Liability to Tax</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Check the 'Liability to Tax' category checkbox
 3. Verify a child category ('Residence') becomes visible</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Checking the 'Liability to Tax' parent category must expand the tree in place to reveal its children (e.g. 'Residence').</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Checking 'Liability to Tax' expanded the category tree, revealing the child category 'Residence'.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'Residence' is hidden before and visible after expanding 'Liability to Tax'</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Information_06</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>WTA Information</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>'Check All' selects every category (not the country list)</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Clicking the 'Check All' checkbox (which sits in the CATEGORY tree, right above the 'Depth-' control) must check every category checkbox, including nested children, while leaving the country checklist untouched.</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on the Information workspace.</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in
-2. Click 'Check All'
-3. Verify the 'Liability to Tax' and a nested child category ('Residence') are both checked
-4. Verify the 'Australia' country checkbox is still unchecked (Check All only affects categories)</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Clicking the 'Check All' checkbox (which sits in the CATEGORY tree, right above the 'Depth-' control) must check every category checkbox, including nested children, while leaving the country checklist untouched.</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Check All' checked every category (including nested children like 'Residence' under 'Liability to Tax') and left the country checklist untouched.</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] 'Liability to Tax' and its child 'Residence' are checked after 'Check All'
-[PASS] 'Australia' remains unchecked - 'Check All' only applies to categories</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
